--- a/WindowsFormsApp1/otchettemplate.xlsx
+++ b/WindowsFormsApp1/otchettemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tchir\OneDrive\Рабочий стол\diplom\diplom\WindowsFormsApp1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D30EE07-7021-459F-9099-2B64820E2E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09148D0F-F03E-4A76-8D2D-2C3CCCA14996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,8 +40,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Номер</t>
   </si>
@@ -111,6 +133,9 @@
   <si>
     <t>Отчет за период:</t>
   </si>
+  <si>
+    <t>Стоматология «Улыбка»</t>
+  </si>
 </sst>
 </file>
 
@@ -119,7 +144,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +193,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF274690"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -198,12 +231,41 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF274690"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF274690"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF274690"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF274690"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF274690"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FF274690"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -211,69 +273,40 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="thick">
+        <color rgb="FF274690"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="thick">
+        <color rgb="FF274690"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="thick">
+        <color rgb="FF274690"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="thick">
+        <color rgb="FF274690"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="thick">
+        <color rgb="FF274690"/>
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="thick">
+        <color rgb="FF274690"/>
       </bottom>
       <diagonal/>
     </border>
@@ -282,16 +315,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -299,25 +324,60 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1730,16 +1790,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>1085850</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>102705</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>139247</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1783,16 +1843,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>178255</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>65314</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1133475</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>112230</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1097528</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>127962</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1824,8 +1884,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3743325" y="228600"/>
-          <a:ext cx="914400" cy="913039"/>
+          <a:off x="11825969" y="1262743"/>
+          <a:ext cx="914400" cy="914572"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1836,9 +1896,9 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="914400" cy="914400"/>
@@ -1883,9 +1943,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="914400" cy="914400"/>
@@ -1930,9 +1990,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>10886</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="914400" cy="914400"/>
@@ -1979,14 +2039,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>16528</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>5347</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>8282</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>92728</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1151283</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>81547</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2013,16 +2073,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>17807</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>20914</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>3727</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>193192</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>97114</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>186566</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2282,6 +2342,70 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2637,50 +2761,50 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="20" style="7" customWidth="1"/>
+    <col min="2" max="2" width="20" style="1" customWidth="1"/>
     <col min="3" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
     <col min="8" max="9" width="12.140625" customWidth="1"/>
     <col min="10" max="10" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2692,15 +2816,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
     <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.42578125" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.42578125" customWidth="1"/>
@@ -2711,120 +2837,184 @@
     <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:12" ht="78" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="12"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="11" t="s">
+    <row r="3" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="13"/>
+      <c r="J3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="1"/>
+      <c r="K3" s="15"/>
     </row>
-    <row r="3" spans="1:15" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A3" s="19"/>
-      <c r="B3" s="6">
+    <row r="4" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I4" s="16"/>
+      <c r="J4" s="17">
         <f>COUNTA(TicketsTable[Номер])</f>
         <v>0</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="6">
+      <c r="K4" s="18"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I5" s="16"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="31"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="28"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="21"/>
+      <c r="J7" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="30"/>
+    </row>
+    <row r="8" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I8" s="21"/>
+      <c r="J8" s="17">
         <f>COUNTIF(TicketsTable[Статус],"*Заверш*")</f>
         <v>0</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="6">
+      <c r="K8" s="18"/>
+    </row>
+    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="I9" s="21"/>
+      <c r="J9" s="22" t="e">
+        <f>J8/J4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="26"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="28"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I11" s="21"/>
+      <c r="J11" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="30"/>
+    </row>
+    <row r="12" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I12" s="21"/>
+      <c r="J12" s="17">
         <f>COUNTIF(TicketsTable[Статус],"*Создан*")</f>
         <v>0</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="6">
+      <c r="K12" s="18"/>
+    </row>
+    <row r="13" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="I13" s="21"/>
+      <c r="J13" s="22" t="e">
+        <f>J12/J4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="26"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="28"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="21"/>
+      <c r="J15" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="30"/>
+    </row>
+    <row r="16" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I16" s="21"/>
+      <c r="J16" s="17">
         <f>COUNTIF(TicketsTable[Статус],"*Отмен*")</f>
         <v>0</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="14">
+      <c r="K16" s="18"/>
+    </row>
+    <row r="17" spans="9:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="I17" s="21"/>
+      <c r="J17" s="22" t="e">
+        <f>J16/J4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K17" s="23"/>
+    </row>
+    <row r="18" spans="9:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="26"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="28"/>
+    </row>
+    <row r="19" spans="9:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I19" s="21"/>
+      <c r="J19" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="30"/>
+    </row>
+    <row r="20" spans="9:11" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I20" s="21"/>
+      <c r="J20" s="24">
         <f>SUMIFS(TicketsTable[Итого],TicketsTable[Статус],"*Заверш*")</f>
         <v>0</v>
       </c>
-      <c r="O3" s="3"/>
+      <c r="K20" s="25"/>
     </row>
-    <row r="4" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="10" t="e">
-        <f>E3/B3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="10" t="e">
-        <f>H3/B3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="10" t="e">
-        <f>K3/B3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="3"/>
+    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I21" s="21"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="20"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="5"/>
+    <row r="22" spans="9:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="26"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="28"/>
     </row>
+    <row r="23" spans="9:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="J2:J5"/>
-    <mergeCell ref="M2:M5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="G2:G5"/>
+  <mergeCells count="18">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="I15:I18"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="I7:I10"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J7:K7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2854,7 +3044,7 @@
       <c r="B1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
@@ -2869,7 +3059,7 @@
         <f>COUNTIF(TicketsTable[Статус],"*Заверш*")</f>
         <v>0</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2881,7 +3071,7 @@
         <f>COUNTIF(TicketsTable[Статус],"*Создан*")</f>
         <v>0</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>19</v>
       </c>
     </row>

--- a/WindowsFormsApp1/otchettemplate.xlsx
+++ b/WindowsFormsApp1/otchettemplate.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tchir\OneDrive\Рабочий стол\diplom\diplom\WindowsFormsApp1\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09148D0F-F03E-4A76-8D2D-2C3CCCA14996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -19,10 +13,10 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="8" r:id="rId4"/>
   </pivotCaches>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,28 +32,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -140,11 +112,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,32 +306,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -368,16 +326,30 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -388,13 +360,13 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -423,18 +395,8 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -476,7 +438,7 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -485,7 +447,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:doughnutChart>
@@ -506,7 +467,6 @@
           </c:tx>
           <c:dPt>
             <c:idx val="0"/>
-            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
@@ -518,7 +478,7 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-8D52-476E-A9E7-8F6D9237B52D}"/>
               </c:ext>
@@ -526,7 +486,6 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
@@ -538,7 +497,7 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-8D52-476E-A9E7-8F6D9237B52D}"/>
               </c:ext>
@@ -546,7 +505,6 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
@@ -558,7 +516,7 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-8D52-476E-A9E7-8F6D9237B52D}"/>
               </c:ext>
@@ -572,14 +530,8 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
@@ -618,20 +570,14 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-8D52-476E-A9E7-8F6D9237B52D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
           <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
         <c:holeSize val="50"/>
@@ -646,7 +592,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:overlay val="0"/>
+      <c:layout/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -677,14 +623,13 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -713,25 +658,15 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageMargins b="0.75000000000000044" l="0.7000000000000004" r="0.7000000000000004" t="0.75000000000000044" header="0.30000000000000021" footer="0.30000000000000021"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[otchettemplate.xlsx]PIVOT!Сводная таблица1</c:name>
     <c:fmtId val="1"/>
@@ -775,7 +710,17 @@
           </a:p>
           <a:p>
             <a:pPr algn="l">
-              <a:defRPr/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU" b="1" baseline="0">
@@ -806,11 +751,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.5034558180227467E-2"/>
+          <c:x val="2.5034558180227477E-2"/>
           <c:y val="2.3148148148148147E-2"/>
         </c:manualLayout>
       </c:layout>
-      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -818,28 +762,7 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l">
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
@@ -857,42 +780,8 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
+          <c:delete val="1"/>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
@@ -943,13 +832,8 @@
             </a:p>
           </c:txPr>
           <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
@@ -960,7 +844,6 @@
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -984,7 +867,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1016,32 +898,7 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -1063,35 +920,27 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-29FC-4BE8-A436-35800C951F3B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="1348859807"/>
-        <c:axId val="1262604015"/>
+        <c:axId val="148239488"/>
+        <c:axId val="179072384"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1348859807"/>
+        <c:axId val="148239488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1126,23 +975,20 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1262604015"/>
+        <c:crossAx val="179072384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1262604015"/>
+        <c:axId val="179072384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1171,7 +1017,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1348859807"/>
+        <c:crossAx val="148239488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1185,14 +1031,13 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1221,10 +1066,10 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst>
+  <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
@@ -1806,7 +1651,7 @@
         <xdr:cNvPr id="4" name="Рисунок 3" descr="Документ контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{739AF3A7-027F-B976-9295-70C4DF1D47DA}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{739AF3A7-027F-B976-9295-70C4DF1D47DA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1818,10 +1663,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -1859,7 +1704,7 @@
         <xdr:cNvPr id="6" name="Рисунок 5" descr="Значок &quot;Галочка1&quot; контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25C503AB-1006-A148-2AB9-AB63A9964A36}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25C503AB-1006-A148-2AB9-AB63A9964A36}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1871,10 +1716,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -1907,7 +1752,7 @@
         <xdr:cNvPr id="7" name="Рисунок 6" descr="Часы контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7693A54A-1D0B-4345-91E0-C5077FEAAD56}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7693A54A-1D0B-4345-91E0-C5077FEAAD56}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1919,10 +1764,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
+              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -1954,7 +1799,7 @@
         <xdr:cNvPr id="8" name="Рисунок 7" descr="Значок &quot;Крестик&quot; контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6758034C-5861-478C-A350-D448B76FCE90}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6758034C-5861-478C-A350-D448B76FCE90}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1966,10 +1811,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId8"/>
+              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId8"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -2001,7 +1846,7 @@
         <xdr:cNvPr id="10" name="Рисунок 9" descr="Рубль контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{476F46BC-6692-44A7-AA2A-56B1754F6588}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{476F46BC-6692-44A7-AA2A-56B1754F6588}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2013,10 +1858,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
+              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -2053,7 +1898,7 @@
         <xdr:cNvPr id="12" name="Диаграмма 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1D906A6-4AA4-2085-822B-955B6482F791}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1D906A6-4AA4-2085-822B-955B6482F791}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2089,7 +1934,7 @@
         <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9252EA80-A8AC-FC6E-450D-E6A8B970528D}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9252EA80-A8AC-FC6E-450D-E6A8B970528D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2107,11 +1952,49 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>154782</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1160859</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>974165</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Рисунок 8" descr="logo3.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4941095" y="0"/>
+          <a:ext cx="1006077" cy="974165"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Dmitriy Chirkov" refreshedDate="46158.568385763887" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{50DB7000-DFBE-483F-92CC-B01789005564}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Dmitriy Chirkov" refreshedDate="46158.568385763887" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10">
   <cacheSource type="worksheet">
     <worksheetSource name="TicketsTable"/>
   </cacheSource>
@@ -2284,7 +2167,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F2AE11D7-8F41-45F6-8155-418E8302AFF5}" name="Сводная таблица1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Врач">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Сводная таблица1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Врач">
   <location ref="D1:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -2409,30 +2292,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TicketsTable" displayName="TicketsTable" ref="A1:J2" insertRow="1" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:J2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TicketsTable" displayName="TicketsTable" ref="A1:J2" insertRow="1" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:J2"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Номер"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Врач" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Дата"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Время"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Регистратор" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Пациент" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Статус"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Сумма"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Скидка"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Итого"/>
+    <tableColumn id="1" name="Номер"/>
+    <tableColumn id="2" name="Врач" dataDxfId="3"/>
+    <tableColumn id="3" name="Дата"/>
+    <tableColumn id="4" name="Время"/>
+    <tableColumn id="5" name="Регистратор" dataDxfId="2"/>
+    <tableColumn id="6" name="Пациент" dataDxfId="1"/>
+    <tableColumn id="7" name="Статус"/>
+    <tableColumn id="8" name="Сумма"/>
+    <tableColumn id="9" name="Скидка"/>
+    <tableColumn id="10" name="Итого"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Таблица2" displayName="Таблица2" ref="A1:B4" totalsRowShown="0">
-  <autoFilter ref="A1:B4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A1:B4" totalsRowShown="0">
+  <autoFilter ref="A1:B4"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Статус"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Кол-во" dataDxfId="0">
+    <tableColumn id="1" name="Статус"/>
+    <tableColumn id="2" name="Кол-во" dataDxfId="0">
       <calculatedColumnFormula>COUNTIF(TicketsTable[Статус],"*Отмен*")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2749,28 +2632,28 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="9" width="12.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="3" max="4" width="12.125" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" customWidth="1"/>
+    <col min="8" max="9" width="12.125" customWidth="1"/>
+    <col min="10" max="10" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2802,7 +2685,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
     </row>
@@ -2815,191 +2698,186 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.375" customWidth="1"/>
+    <col min="2" max="2" width="25.75" customWidth="1"/>
+    <col min="3" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="4" width="19.375" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="19.375" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.375" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" customWidth="1"/>
-    <col min="14" max="14" width="42.85546875" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" customWidth="1"/>
+    <col min="13" max="13" width="19.375" customWidth="1"/>
+    <col min="14" max="14" width="42.875" customWidth="1"/>
+    <col min="16" max="16" width="19.375" customWidth="1"/>
     <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.42578125" customWidth="1"/>
+    <col min="21" max="21" width="19.375" customWidth="1"/>
     <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="78" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:12" ht="78" customHeight="1" thickBot="1">
+      <c r="A1" s="9"/>
+      <c r="B1" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="12"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="11"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="I3" s="13"/>
-      <c r="J3" s="14" t="s">
+    <row r="3" spans="1:12" ht="16.5" thickTop="1">
+      <c r="I3" s="12"/>
+      <c r="J3" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="15"/>
+      <c r="K3" s="29"/>
     </row>
-    <row r="4" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="I4" s="16"/>
-      <c r="J4" s="17">
+    <row r="4" spans="1:12" ht="30">
+      <c r="I4" s="13"/>
+      <c r="J4" s="24">
         <f>COUNTA(TicketsTable[Номер])</f>
         <v>0</v>
       </c>
-      <c r="K4" s="18"/>
+      <c r="K4" s="25"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I5" s="16"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="20"/>
+    <row r="5" spans="1:12">
+      <c r="I5" s="13"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="15"/>
     </row>
-    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I6" s="31"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="28"/>
+    <row r="6" spans="1:12" ht="15" thickBot="1">
+      <c r="I6" s="18"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="17"/>
     </row>
-    <row r="7" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="I7" s="21"/>
-      <c r="J7" s="29" t="s">
+    <row r="7" spans="1:12" ht="16.5" thickTop="1">
+      <c r="I7" s="19"/>
+      <c r="J7" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="30"/>
+      <c r="K7" s="27"/>
     </row>
-    <row r="8" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="I8" s="21"/>
-      <c r="J8" s="17">
+    <row r="8" spans="1:12" ht="30">
+      <c r="I8" s="19"/>
+      <c r="J8" s="24">
         <f>COUNTIF(TicketsTable[Статус],"*Заверш*")</f>
         <v>0</v>
       </c>
-      <c r="K8" s="18"/>
+      <c r="K8" s="25"/>
     </row>
-    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="I9" s="21"/>
-      <c r="J9" s="22" t="e">
+    <row r="9" spans="1:12" ht="18">
+      <c r="I9" s="19"/>
+      <c r="J9" s="30" t="e">
         <f>J8/J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K9" s="23"/>
+      <c r="K9" s="31"/>
     </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I10" s="26"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="28"/>
+    <row r="10" spans="1:12" ht="15" thickBot="1">
+      <c r="I10" s="20"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="17"/>
     </row>
-    <row r="11" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="I11" s="21"/>
-      <c r="J11" s="29" t="s">
+    <row r="11" spans="1:12" ht="16.5" thickTop="1">
+      <c r="I11" s="19"/>
+      <c r="J11" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="30"/>
+      <c r="K11" s="27"/>
     </row>
-    <row r="12" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="I12" s="21"/>
-      <c r="J12" s="17">
+    <row r="12" spans="1:12" ht="30">
+      <c r="I12" s="19"/>
+      <c r="J12" s="24">
         <f>COUNTIF(TicketsTable[Статус],"*Создан*")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="18"/>
+      <c r="K12" s="25"/>
     </row>
-    <row r="13" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="I13" s="21"/>
-      <c r="J13" s="22" t="e">
+    <row r="13" spans="1:12" ht="18">
+      <c r="I13" s="19"/>
+      <c r="J13" s="30" t="e">
         <f>J12/J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="31"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I14" s="26"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="28"/>
+    <row r="14" spans="1:12" ht="15" thickBot="1">
+      <c r="I14" s="20"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="17"/>
     </row>
-    <row r="15" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="I15" s="21"/>
-      <c r="J15" s="29" t="s">
+    <row r="15" spans="1:12" ht="16.5" thickTop="1">
+      <c r="I15" s="19"/>
+      <c r="J15" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="30"/>
+      <c r="K15" s="27"/>
     </row>
-    <row r="16" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="I16" s="21"/>
-      <c r="J16" s="17">
+    <row r="16" spans="1:12" ht="30">
+      <c r="I16" s="19"/>
+      <c r="J16" s="24">
         <f>COUNTIF(TicketsTable[Статус],"*Отмен*")</f>
         <v>0</v>
       </c>
-      <c r="K16" s="18"/>
+      <c r="K16" s="25"/>
     </row>
-    <row r="17" spans="9:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="I17" s="21"/>
-      <c r="J17" s="22" t="e">
+    <row r="17" spans="9:11" ht="18">
+      <c r="I17" s="19"/>
+      <c r="J17" s="30" t="e">
         <f>J16/J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K17" s="23"/>
+      <c r="K17" s="31"/>
     </row>
-    <row r="18" spans="9:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I18" s="26"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="28"/>
+    <row r="18" spans="9:11" ht="15" thickBot="1">
+      <c r="I18" s="20"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="9:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="I19" s="21"/>
-      <c r="J19" s="29" t="s">
+    <row r="19" spans="9:11" ht="16.5" thickTop="1">
+      <c r="I19" s="19"/>
+      <c r="J19" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="K19" s="30"/>
+      <c r="K19" s="27"/>
     </row>
-    <row r="20" spans="9:11" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="I20" s="21"/>
-      <c r="J20" s="24">
+    <row r="20" spans="9:11" ht="30">
+      <c r="I20" s="19"/>
+      <c r="J20" s="22">
         <f>SUMIFS(TicketsTable[Итого],TicketsTable[Статус],"*Заверш*")</f>
         <v>0</v>
       </c>
-      <c r="K20" s="25"/>
+      <c r="K20" s="23"/>
     </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I21" s="21"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="20"/>
+    <row r="21" spans="9:11">
+      <c r="I21" s="19"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="15"/>
     </row>
-    <row r="22" spans="9:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I22" s="26"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="28"/>
+    <row r="22" spans="9:11" ht="15" thickBot="1">
+      <c r="I22" s="20"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="17"/>
     </row>
-    <row r="23" spans="9:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="9:11" ht="15" thickTop="1"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J13:K13"/>
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="I15:I18"/>
     <mergeCell ref="I19:I22"/>
@@ -3015,6 +2893,9 @@
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="J11:K11"/>
     <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J13:K13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3023,21 +2904,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -3051,7 +2932,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3063,7 +2944,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3075,7 +2956,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>17</v>
       </c>

--- a/WindowsFormsApp1/otchettemplate.xlsx
+++ b/WindowsFormsApp1/otchettemplate.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tchir\OneDrive\Рабочий стол\diplom\diplom\WindowsFormsApp1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FDAD22-787F-453B-BC9D-7DC086AD49A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -13,10 +19,10 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -112,11 +118,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,7 +165,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="20"/>
       <color rgb="FF274690"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -167,7 +173,7 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="14"/>
       <color rgb="FF274690"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -287,7 +293,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -302,7 +308,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -310,29 +315,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -350,6 +355,8 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -360,13 +367,13 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -395,8 +402,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -438,7 +455,7 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -447,6 +464,7 @@
         <a:effectLst/>
       </c:spPr>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:doughnutChart>
@@ -467,6 +485,7 @@
           </c:tx>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
@@ -478,7 +497,7 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-8D52-476E-A9E7-8F6D9237B52D}"/>
               </c:ext>
@@ -486,6 +505,7 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
@@ -497,7 +517,7 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-8D52-476E-A9E7-8F6D9237B52D}"/>
               </c:ext>
@@ -505,6 +525,7 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
@@ -516,7 +537,7 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-8D52-476E-A9E7-8F6D9237B52D}"/>
               </c:ext>
@@ -530,8 +551,14 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
@@ -570,14 +597,20 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-8D52-476E-A9E7-8F6D9237B52D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
           <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
         <c:holeSize val="50"/>
@@ -592,7 +625,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -623,13 +656,14 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -665,8 +699,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[otchettemplate.xlsx]PIVOT!Сводная таблица1</c:name>
     <c:fmtId val="1"/>
@@ -710,17 +754,7 @@
           </a:p>
           <a:p>
             <a:pPr algn="l">
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU" b="1" baseline="0">
@@ -755,6 +789,7 @@
           <c:y val="2.3148148148148147E-2"/>
         </c:manualLayout>
       </c:layout>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -762,7 +797,28 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
@@ -780,8 +836,13 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:delete val="1"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
@@ -832,8 +893,13 @@
             </a:p>
           </c:txPr>
           <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
@@ -844,6 +910,7 @@
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -867,6 +934,7 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -898,7 +966,18 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -920,14 +999,19 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-29FC-4BE8-A436-35800C951F3B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
         <c:axId val="148239488"/>
@@ -938,9 +1022,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -980,15 +1066,18 @@
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="179072384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1031,13 +1120,14 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1069,7 +1159,7 @@
     <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:extLst>
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
@@ -1651,7 +1741,7 @@
         <xdr:cNvPr id="4" name="Рисунок 3" descr="Документ контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{739AF3A7-027F-B976-9295-70C4DF1D47DA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1663,10 +1753,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -1704,7 +1794,7 @@
         <xdr:cNvPr id="6" name="Рисунок 5" descr="Значок &quot;Галочка1&quot; контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25C503AB-1006-A148-2AB9-AB63A9964A36}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1716,10 +1806,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -1752,7 +1842,7 @@
         <xdr:cNvPr id="7" name="Рисунок 6" descr="Часы контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7693A54A-1D0B-4345-91E0-C5077FEAAD56}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1764,10 +1854,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -1799,7 +1889,7 @@
         <xdr:cNvPr id="8" name="Рисунок 7" descr="Значок &quot;Крестик&quot; контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6758034C-5861-478C-A350-D448B76FCE90}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1811,10 +1901,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId8"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId8"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -1846,7 +1936,7 @@
         <xdr:cNvPr id="10" name="Рисунок 9" descr="Рубль контур">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{476F46BC-6692-44A7-AA2A-56B1754F6588}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1858,10 +1948,10 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -1883,22 +1973,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>5347</xdr:rowOff>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>195846</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1151283</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>81547</xdr:rowOff>
+      <xdr:colOff>1162489</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>25517</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="12" name="Диаграмма 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1D906A6-4AA4-2085-822B-955B6482F791}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1919,22 +2009,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3727</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>193192</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>13899</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>186566</xdr:rowOff>
+      <xdr:colOff>926361</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9252EA80-A8AC-FC6E-450D-E6A8B970528D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1967,7 +2057,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Рисунок 8" descr="logo3.png"/>
+        <xdr:cNvPr id="9" name="Рисунок 8" descr="logo3.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1994,7 +2090,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Dmitriy Chirkov" refreshedDate="46158.568385763887" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Dmitriy Chirkov" refreshedDate="46158.568385763887" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{00000000-000A-0000-FFFF-FFFF08000000}">
   <cacheSource type="worksheet">
     <worksheetSource name="TicketsTable"/>
   </cacheSource>
@@ -2167,7 +2263,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Сводная таблица1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Врач">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Сводная таблица1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Врач">
   <location ref="D1:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -2227,95 +2323,31 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TicketsTable" displayName="TicketsTable" ref="A1:J2" insertRow="1" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:J2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TicketsTable" displayName="TicketsTable" ref="A1:J2" insertRow="1" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:J2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="Номер"/>
-    <tableColumn id="2" name="Врач" dataDxfId="3"/>
-    <tableColumn id="3" name="Дата"/>
-    <tableColumn id="4" name="Время"/>
-    <tableColumn id="5" name="Регистратор" dataDxfId="2"/>
-    <tableColumn id="6" name="Пациент" dataDxfId="1"/>
-    <tableColumn id="7" name="Статус"/>
-    <tableColumn id="8" name="Сумма"/>
-    <tableColumn id="9" name="Скидка"/>
-    <tableColumn id="10" name="Итого"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Номер"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Врач" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Дата"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Время"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Регистратор" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Пациент" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Статус"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Сумма"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Скидка"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Итого"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A1:B4" totalsRowShown="0">
-  <autoFilter ref="A1:B4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Таблица2" displayName="Таблица2" ref="A1:B4" totalsRowShown="0">
+  <autoFilter ref="A1:B4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Статус"/>
-    <tableColumn id="2" name="Кол-во" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Статус"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Кол-во" dataDxfId="0">
       <calculatedColumnFormula>COUNTIF(TicketsTable[Статус],"*Отмен*")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2632,28 +2664,28 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12.125" customWidth="1"/>
-    <col min="5" max="5" width="21.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" customWidth="1"/>
-    <col min="8" max="9" width="12.125" customWidth="1"/>
-    <col min="10" max="10" width="13.125" customWidth="1"/>
+    <col min="3" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="9" width="12.140625" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2685,7 +2717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
     </row>
@@ -2698,189 +2730,187 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.375" customWidth="1"/>
-    <col min="2" max="2" width="25.75" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="19.375" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.375" customWidth="1"/>
-    <col min="14" max="14" width="42.875" customWidth="1"/>
-    <col min="16" max="16" width="19.375" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" customWidth="1"/>
+    <col min="14" max="14" width="42.85546875" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" customWidth="1"/>
     <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.375" customWidth="1"/>
+    <col min="21" max="21" width="19.42578125" customWidth="1"/>
     <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="78" customHeight="1" thickBot="1">
-      <c r="A1" s="9"/>
-      <c r="B1" s="21" t="s">
+    <row r="1" spans="1:12" ht="78" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8"/>
+      <c r="B1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="11"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="10"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:12" ht="28.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
         <v>22</v>
       </c>
+      <c r="B2" s="19"/>
     </row>
-    <row r="3" spans="1:12" ht="16.5" thickTop="1">
-      <c r="I3" s="12"/>
-      <c r="J3" s="28" t="s">
+    <row r="3" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="11"/>
+      <c r="J3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="29"/>
+      <c r="K3" s="28"/>
     </row>
-    <row r="4" spans="1:12" ht="30">
-      <c r="I4" s="13"/>
-      <c r="J4" s="24">
+    <row r="4" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I4" s="12"/>
+      <c r="J4" s="23">
         <f>COUNTA(TicketsTable[Номер])</f>
         <v>0</v>
       </c>
-      <c r="K4" s="25"/>
+      <c r="K4" s="24"/>
     </row>
-    <row r="5" spans="1:12">
-      <c r="I5" s="13"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="15"/>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I5" s="12"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="14"/>
     </row>
-    <row r="6" spans="1:12" ht="15" thickBot="1">
-      <c r="I6" s="18"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17"/>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="17"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:12" ht="16.5" thickTop="1">
-      <c r="I7" s="19"/>
-      <c r="J7" s="26" t="s">
+    <row r="7" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="31"/>
+      <c r="J7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="27"/>
+      <c r="K7" s="26"/>
     </row>
-    <row r="8" spans="1:12" ht="30">
-      <c r="I8" s="19"/>
-      <c r="J8" s="24">
+    <row r="8" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I8" s="31"/>
+      <c r="J8" s="23">
         <f>COUNTIF(TicketsTable[Статус],"*Заверш*")</f>
         <v>0</v>
       </c>
-      <c r="K8" s="25"/>
+      <c r="K8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="18">
-      <c r="I9" s="19"/>
-      <c r="J9" s="30" t="e">
+    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="I9" s="31"/>
+      <c r="J9" s="29" t="e">
         <f>J8/J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K9" s="31"/>
+      <c r="K9" s="30"/>
     </row>
-    <row r="10" spans="1:12" ht="15" thickBot="1">
-      <c r="I10" s="20"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="17"/>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="32"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
     </row>
-    <row r="11" spans="1:12" ht="16.5" thickTop="1">
-      <c r="I11" s="19"/>
-      <c r="J11" s="26" t="s">
+    <row r="11" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I11" s="31"/>
+      <c r="J11" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="26"/>
     </row>
-    <row r="12" spans="1:12" ht="30">
-      <c r="I12" s="19"/>
-      <c r="J12" s="24">
+    <row r="12" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I12" s="31"/>
+      <c r="J12" s="23">
         <f>COUNTIF(TicketsTable[Статус],"*Создан*")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="25"/>
+      <c r="K12" s="24"/>
     </row>
-    <row r="13" spans="1:12" ht="18">
-      <c r="I13" s="19"/>
-      <c r="J13" s="30" t="e">
+    <row r="13" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="I13" s="31"/>
+      <c r="J13" s="29" t="e">
         <f>J12/J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K13" s="31"/>
+      <c r="K13" s="30"/>
     </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1">
-      <c r="I14" s="20"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="17"/>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="32"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="16"/>
     </row>
-    <row r="15" spans="1:12" ht="16.5" thickTop="1">
-      <c r="I15" s="19"/>
-      <c r="J15" s="26" t="s">
+    <row r="15" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="31"/>
+      <c r="J15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="27"/>
+      <c r="K15" s="26"/>
     </row>
-    <row r="16" spans="1:12" ht="30">
-      <c r="I16" s="19"/>
-      <c r="J16" s="24">
+    <row r="16" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I16" s="31"/>
+      <c r="J16" s="23">
         <f>COUNTIF(TicketsTable[Статус],"*Отмен*")</f>
         <v>0</v>
       </c>
-      <c r="K16" s="25"/>
+      <c r="K16" s="24"/>
     </row>
-    <row r="17" spans="9:11" ht="18">
-      <c r="I17" s="19"/>
-      <c r="J17" s="30" t="e">
+    <row r="17" spans="9:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="I17" s="31"/>
+      <c r="J17" s="29" t="e">
         <f>J16/J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K17" s="31"/>
+      <c r="K17" s="30"/>
     </row>
-    <row r="18" spans="9:11" ht="15" thickBot="1">
-      <c r="I18" s="20"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="17"/>
+    <row r="18" spans="9:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="32"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="16"/>
     </row>
-    <row r="19" spans="9:11" ht="16.5" thickTop="1">
-      <c r="I19" s="19"/>
-      <c r="J19" s="26" t="s">
+    <row r="19" spans="9:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I19" s="31"/>
+      <c r="J19" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="K19" s="27"/>
+      <c r="K19" s="26"/>
     </row>
-    <row r="20" spans="9:11" ht="30">
-      <c r="I20" s="19"/>
-      <c r="J20" s="22">
+    <row r="20" spans="9:11" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I20" s="31"/>
+      <c r="J20" s="21">
         <f>SUMIFS(TicketsTable[Итого],TicketsTable[Статус],"*Заверш*")</f>
         <v>0</v>
       </c>
-      <c r="K20" s="23"/>
+      <c r="K20" s="22"/>
     </row>
-    <row r="21" spans="9:11">
-      <c r="I21" s="19"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="15"/>
+    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I21" s="31"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="14"/>
     </row>
-    <row r="22" spans="9:11" ht="15" thickBot="1">
-      <c r="I22" s="20"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="17"/>
+    <row r="22" spans="9:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="32"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="9:11" ht="15" thickTop="1"/>
+    <row r="23" spans="9:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="I15:I18"/>
-    <mergeCell ref="I19:I22"/>
     <mergeCell ref="I7:I10"/>
     <mergeCell ref="I11:I14"/>
     <mergeCell ref="B1:J1"/>
@@ -2896,6 +2926,9 @@
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="I15:I18"/>
+    <mergeCell ref="I19:I22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2904,21 +2937,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2932,7 +2965,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -2944,7 +2977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2956,7 +2989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
